--- a/exports/colleges/25469_school-of-planning-and-architecture-spa-new-delhi.xlsx
+++ b/exports/colleges/25469_school-of-planning-and-architecture-spa-new-delhi.xlsx
@@ -605,19 +605,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="47" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
     <col width="47" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="35" customWidth="1" min="8" max="8"/>
     <col width="23" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
   </cols>
@@ -692,7 +692,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>B.Arch</t>
+          <t>Bachelor of Architecture [B.Arch]</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -702,17 +702,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Bachelor of Architecture [B.Arch]</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4.21 Lakhs</t>
+          <t>4.21 L</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>5 Years</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -722,17 +722,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>10+2 +JEE Mains</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>JEE Main, NATA, DASA</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>2 June - 11 Jun 2026</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>M.Arch</t>
+          <t>Master of Architecture [M.Arch]</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -764,17 +764,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Master of Architecture [M.Arch]</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2.42 Lakhs</t>
+          <t>2.42 L</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Graduation+ GATE/CEED/ UGCNet</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>15 May - 04 Aug 2026</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>B.Planning</t>
+          <t>Bachelor of Planning</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -826,17 +826,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Bachelor of Planning</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>4.22 Lakhs</t>
+          <t>4.22 L</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -846,17 +846,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>10+2+JEE MAINS</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>JEE Main</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>2 June - 11 Jun 2026</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2.42 Lakhs</t>
+          <t>2.42 L</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -908,17 +908,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Graduation</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>CEED</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>6 May - 30 May 2026</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M.Planning</t>
+          <t>Master of Planning</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -950,17 +950,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Master of Planning</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2.42 Lakhs</t>
+          <t>2.42 L</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Graduation</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>15 May - 04 Aug 2026</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -1002,27 +1002,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>B.Arch</t>
+          <t>Master of Planning [M.Plan] (Urban Planning)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B.Arch</t>
+          <t>Master of Planning [M.Plan] (Urban Planning)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>B.Arch</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>4.21 Lakhs</t>
+          <t>2.42 L</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>15 May - 04 Aug 2026</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1064,27 +1064,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>M.Arch</t>
+          <t>Master of Building Engineering and Management</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>M.Arch</t>
+          <t>Master of Building Engineering and Management</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>M.Arch</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2.42 Lakhs</t>
+          <t>2.42 L</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>15 May - 04 Aug 2026</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1126,27 +1126,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>B.Plan</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B.Plan</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>B.Plan</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>4.22 Lakhs</t>
+          <t>1.12 L</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>GATE / UGC NET</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>30 June 2025</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -1188,27 +1188,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>M.Plan</t>
+          <t>B.Arch</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>M.Plan</t>
+          <t>Bachelor of Architecture [B.Arch]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>M.Plan</t>
+          <t>Bachelor of Architecture [B.Arch]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2.42 Lakhs</t>
+          <t>4.21 Lakhs</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>5 Years</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>10+2 +JEE Mains</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>JEE Main, NATA, DASA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1250,17 +1250,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>M.Des</t>
+          <t>M.Arch</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>M.Des</t>
+          <t>Master of Architecture [M.Arch]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>M.Des</t>
+          <t>Master of Architecture [M.Arch]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1280,12 +1280,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation+ GATE/CEED/ UGCNet</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>CEED</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1312,27 +1312,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>B.Planning</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>Bachelor of Planning</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>Bachelor of Planning</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.12 Lakhs</t>
+          <t>4.22 Lakhs</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>3-5 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1342,12 +1342,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>10+2+JEE MAINS</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>GATE / UGC NET</t>
+          <t>JEE Main</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Doctorate</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -1374,17 +1374,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>M.Arch Landscape Architecture</t>
+          <t>M.Des</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>M.Arch Landscape Architecture</t>
+          <t>Master of Design [M.Des] (Industrial Design)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>M.Arch Landscape Architecture</t>
+          <t>Master of Design [M.Des] (Industrial Design)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -1436,17 +1436,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>M.Arch Urban Design</t>
+          <t>M.Planning</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>M.Arch Urban Design</t>
+          <t>Master of Planning</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>M.Arch Urban Design</t>
+          <t>Master of Planning</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -1498,22 +1498,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>M.Arch Architectural Conservation</t>
+          <t>B.Arch</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>M.Arch Architectural Conservation</t>
+          <t>B.Arch</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>M.Arch Architectural Conservation</t>
+          <t>B.Arch</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2.42 Lakhs</t>
+          <t>4.21 Lakhs</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1560,17 +1560,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>M.Plan</t>
+          <t>M.Arch</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>M.Plan (General)</t>
+          <t>M.Arch</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>M.Arch</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1578,7 +1578,11 @@
           <t>2.42 Lakhs</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>Full Time</t>
@@ -1618,27 +1622,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>M.Des</t>
+          <t>B.Plan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>M.Des (General)</t>
+          <t>B.Plan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>B.Plan</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2.42 Lakhs</t>
+          <t>4.22 Lakhs</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1653,7 +1657,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>CEED</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1668,7 +1672,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -1680,27 +1684,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>M.Plan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ph.D (General)</t>
+          <t>M.Plan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>M.Plan</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.12 Lakhs</t>
+          <t>2.42 Lakhs</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>3-5 Years</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1715,7 +1719,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>GATE / UGC NET</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1730,7 +1734,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Doctorate</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -1742,27 +1746,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>M.Des</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>M.Des</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>M.Des</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3.4 Lakhs</t>
+          <t>2.42 Lakhs</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>3-5 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1772,12 +1776,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Postgraduation in relevant field</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>GATE / UGC NET</t>
+          <t>CEED</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1792,7 +1796,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Doctorate</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -1809,17 +1813,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>3.4 Lakhs</t>
+          <t>1.12 Lakhs</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1834,7 +1838,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Postgraduation in relevant field</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1866,27 +1870,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>M.Arch Landscape Architecture</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Humanities And Social Science</t>
+          <t>M.Arch Landscape Architecture</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Humanities And Social Science</t>
+          <t>M.Arch Landscape Architecture</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>3.4 Lakhs</t>
+          <t>2.42 Lakhs</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>3-5 Years</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1896,12 +1900,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Postgraduation in relevant field</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>GATE / UGC NET</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1916,7 +1920,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Doctorate</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -1928,55 +1932,547 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>M.Arch Urban Design</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>M.Arch Urban Design</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>M.Arch Urban Design</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2.42 Lakhs</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>25469</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>M.Arch Architectural Conservation</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>M.Arch Architectural Conservation</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>M.Arch Architectural Conservation</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2.42 Lakhs</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>25469</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>M.Plan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>M.Plan (General)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2.42 Lakhs</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>25469</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>M.Des</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>M.Des (General)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2.42 Lakhs</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>CEED</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>25469</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>Ph.D</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ph.D (General)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1.12 Lakhs</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>3-5 Years</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>GATE / UGC NET</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Doctorate</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>25469</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Ph.D</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>3.4 Lakhs</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>3-5 Years</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Postgraduation in relevant field</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>GATE / UGC NET</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Doctorate</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>25469</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Ph.D</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>3.4 Lakhs</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>3-5 Years</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Postgraduation in relevant field</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>GATE / UGC NET</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Doctorate</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>25469</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Ph.D</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Humanities And Social Science</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Humanities And Social Science</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>3.4 Lakhs</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>3-5 Years</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Postgraduation in relevant field</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>GATE / UGC NET</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Doctorate</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>25469</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Ph.D</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
         <is>
           <t>Public Policy</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>Public Policy</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>3.4 Lakhs</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>3-5 Years</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>Full Time</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>Postgraduation in relevant field</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>GATE / UGC NET</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t>Doctorate</t>
         </is>
